--- a/PCB/TestPoint_PCB1_2026-08-11.xlsx
+++ b/PCB/TestPoint_PCB1_2026-08-11.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>Nets Total</t>
   </si>
@@ -48,142 +48,151 @@
     <t>Quanatity</t>
   </si>
   <si>
+    <t>$1N473</t>
+  </si>
+  <si>
     <t>$1N456</t>
   </si>
   <si>
+    <t>$1N406</t>
+  </si>
+  <si>
+    <t>$1N409</t>
+  </si>
+  <si>
     <t>$1N405</t>
   </si>
   <si>
+    <t>$1N391</t>
+  </si>
+  <si>
+    <t>$1N387</t>
+  </si>
+  <si>
+    <t>$1N439</t>
+  </si>
+  <si>
+    <t>$1N470</t>
+  </si>
+  <si>
+    <t>$1N371</t>
+  </si>
+  <si>
+    <t>$1N404</t>
+  </si>
+  <si>
+    <t>$1N462</t>
+  </si>
+  <si>
+    <t>$1N464</t>
+  </si>
+  <si>
+    <t>$1N399</t>
+  </si>
+  <si>
+    <t>$1N378</t>
+  </si>
+  <si>
+    <t>$1N388</t>
+  </si>
+  <si>
+    <t>$1N401</t>
+  </si>
+  <si>
+    <t>$1N398</t>
+  </si>
+  <si>
+    <t>$1N403</t>
+  </si>
+  <si>
+    <t>$1N402</t>
+  </si>
+  <si>
+    <t>$1N400</t>
+  </si>
+  <si>
+    <t>$1N370</t>
+  </si>
+  <si>
+    <t>$1N425</t>
+  </si>
+  <si>
+    <t>$1N444</t>
+  </si>
+  <si>
+    <t>$1N424</t>
+  </si>
+  <si>
+    <t>$1N452</t>
+  </si>
+  <si>
+    <t>$1N451</t>
+  </si>
+  <si>
+    <t>$1N392</t>
+  </si>
+  <si>
+    <t>$1N450</t>
+  </si>
+  <si>
+    <t>$1N449</t>
+  </si>
+  <si>
+    <t>$1N453</t>
+  </si>
+  <si>
+    <t>$1N384</t>
+  </si>
+  <si>
+    <t>$1N438</t>
+  </si>
+  <si>
+    <t>$1N394</t>
+  </si>
+  <si>
+    <t>$1N360</t>
+  </si>
+  <si>
+    <t>$1N368</t>
+  </si>
+  <si>
+    <t>$1N379</t>
+  </si>
+  <si>
+    <t>$1N373</t>
+  </si>
+  <si>
+    <t>$1N395</t>
+  </si>
+  <si>
+    <t>$1N380</t>
+  </si>
+  <si>
+    <t>$1N359</t>
+  </si>
+  <si>
+    <t>$1N357</t>
+  </si>
+  <si>
+    <t>$1N471</t>
+  </si>
+  <si>
+    <t>$1N465</t>
+  </si>
+  <si>
+    <t>$1N433</t>
+  </si>
+  <si>
     <t>$1N460</t>
   </si>
   <si>
-    <t>$1N418</t>
-  </si>
-  <si>
-    <t>$1N406</t>
-  </si>
-  <si>
-    <t>$1N391</t>
-  </si>
-  <si>
-    <t>$1N387</t>
-  </si>
-  <si>
-    <t>$1N439</t>
-  </si>
-  <si>
-    <t>$1N371</t>
-  </si>
-  <si>
-    <t>$1N435</t>
-  </si>
-  <si>
-    <t>$1N388</t>
-  </si>
-  <si>
-    <t>$1N399</t>
-  </si>
-  <si>
-    <t>$1N398</t>
-  </si>
-  <si>
-    <t>$1N402</t>
-  </si>
-  <si>
-    <t>$1N401</t>
-  </si>
-  <si>
-    <t>$1N403</t>
-  </si>
-  <si>
-    <t>$1N400</t>
-  </si>
-  <si>
-    <t>$1N370</t>
-  </si>
-  <si>
-    <t>$1N378</t>
-  </si>
-  <si>
-    <t>$1N425</t>
-  </si>
-  <si>
-    <t>$1N444</t>
-  </si>
-  <si>
-    <t>$1N424</t>
-  </si>
-  <si>
-    <t>$1N451</t>
-  </si>
-  <si>
-    <t>$1N392</t>
-  </si>
-  <si>
-    <t>$1N452</t>
-  </si>
-  <si>
-    <t>$1N450</t>
-  </si>
-  <si>
-    <t>$1N449</t>
-  </si>
-  <si>
-    <t>$1N438</t>
-  </si>
-  <si>
-    <t>$1N394</t>
-  </si>
-  <si>
     <t>$1N393</t>
   </si>
   <si>
-    <t>$1N384</t>
-  </si>
-  <si>
-    <t>$1N368</t>
-  </si>
-  <si>
-    <t>$1N360</t>
-  </si>
-  <si>
-    <t>$1N373</t>
-  </si>
-  <si>
-    <t>$1N379</t>
-  </si>
-  <si>
-    <t>$1N380</t>
-  </si>
-  <si>
-    <t>$1N359</t>
-  </si>
-  <si>
-    <t>$1N357</t>
-  </si>
-  <si>
-    <t>$1N448</t>
-  </si>
-  <si>
-    <t>$1N457</t>
-  </si>
-  <si>
-    <t>$1N433</t>
-  </si>
-  <si>
-    <t>$1N404</t>
-  </si>
-  <si>
-    <t>$1N409</t>
-  </si>
-  <si>
-    <t>$1N395</t>
-  </si>
-  <si>
-    <t>$1N453</t>
-  </si>
-  <si>
     <t>$1N413</t>
+  </si>
+  <si>
+    <t>$1N472</t>
   </si>
   <si>
     <t>Number</t>
@@ -591,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -607,7 +616,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -659,7 +668,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1035,6 +1044,30 @@
         <v>56</v>
       </c>
       <c r="B47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50">
         <v>0</v>
       </c>
     </row>
@@ -1052,22 +1085,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
